--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486914_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486914_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. LOPEZ-SANVICENTE RETA</t>
+          <t>J. FRITZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.722099999999999</v>
+        <v>8.7334</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7974</v>
+        <v>7.8218</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9246</v>
+        <v>0.9116</v>
       </c>
       <c r="G2" t="n">
-        <v>6.1963</v>
+        <v>3.8405</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9761</v>
+        <v>1.5408</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2202</v>
+        <v>2.2997</v>
       </c>
       <c r="J2" t="n">
-        <v>6.0792</v>
+        <v>3.479</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2775</v>
+        <v>2.2031</v>
       </c>
       <c r="L2" t="n">
-        <v>3.8017</v>
+        <v>1.2759</v>
       </c>
       <c r="M2" t="n">
-        <v>0.117</v>
+        <v>0.3615</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.3014</v>
+        <v>-0.6623</v>
       </c>
       <c r="O2" t="n">
-        <v>1.4185</v>
+        <v>1.0238</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R2" t="n">
         <v>2.2588</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2301</v>
+        <v>1.1516</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4411</v>
+        <v>0.8522</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7891</v>
+        <v>0.2995</v>
       </c>
       <c r="V2" t="n">
-        <v>2.117</v>
+        <v>3.5359</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3573</v>
+        <v>5.5441</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2402</v>
+        <v>-2.0082</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. FRITZ</t>
+          <t>P. LOPEZ-SANVICENTE RETA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.6305</v>
+        <v>8.5749</v>
       </c>
       <c r="E3" t="n">
-        <v>7.9264</v>
+        <v>6.0652</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7040999999999999</v>
+        <v>2.5097</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8405</v>
+        <v>6.1963</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5408</v>
+        <v>0.9761</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2997</v>
+        <v>5.2202</v>
       </c>
       <c r="J3" t="n">
-        <v>3.479</v>
+        <v>6.0792</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2031</v>
+        <v>2.2775</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2759</v>
+        <v>3.8017</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3615</v>
+        <v>0.117</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6623</v>
+        <v>-1.3014</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0238</v>
+        <v>1.4185</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2053</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R3" t="n">
         <v>2.2588</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0488</v>
+        <v>1.0829</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9568</v>
+        <v>0.7088</v>
       </c>
       <c r="U3" t="n">
-        <v>0.092</v>
+        <v>0.3741</v>
       </c>
       <c r="V3" t="n">
-        <v>3.5359</v>
+        <v>2.117</v>
       </c>
       <c r="W3" t="n">
-        <v>5.5441</v>
+        <v>2.3573</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.0082</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7705</v>
+        <v>3.0439</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1888</v>
+        <v>0.2547</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5817</v>
+        <v>2.7892</v>
       </c>
       <c r="G4" t="n">
         <v>3.5307</v>
@@ -766,13 +766,13 @@
         <v>2.0534</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7039</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4298</v>
+        <v>0.4957</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2741</v>
+        <v>0.4816</v>
       </c>
       <c r="V4" t="n">
         <v>0.5893</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2124</v>
+        <v>2.5559</v>
       </c>
       <c r="E5" t="n">
-        <v>1.138</v>
+        <v>1.4518</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0744</v>
+        <v>1.1041</v>
       </c>
       <c r="G5" t="n">
         <v>0.484</v>
@@ -844,13 +844,13 @@
         <v>2.4641</v>
       </c>
       <c r="S5" t="n">
-        <v>0.291</v>
+        <v>0.6344</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4806</v>
+        <v>-0.1668</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7716</v>
+        <v>0.8012</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ SOLER</t>
+          <t>O. BIESHAAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6411</v>
+        <v>1.6922</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2753</v>
+        <v>0.7402</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3657</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.54</v>
+        <v>0.4323</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4768</v>
+        <v>0.8139</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06320000000000001</v>
+        <v>-0.3816</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2604</v>
+        <v>1.418</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9183</v>
+        <v>1.6157</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6579</v>
+        <v>-0.1977</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2796</v>
+        <v>-0.9856</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4415</v>
+        <v>-0.8017</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7211</v>
+        <v>-0.1839</v>
       </c>
       <c r="P6" t="n">
-        <v>0.616</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
-        <v>0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="S6" t="n">
-        <v>1.6636</v>
+        <v>0.5269</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0149</v>
+        <v>-0.2404</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.7673</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1786</v>
+        <v>0.9384</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1786</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. BIESHAAR</t>
+          <t>G. RODRIGUEZ SOLER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8942</v>
+        <v>1.4632</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0579</v>
+        <v>1.2753</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.1879</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4323</v>
+        <v>0.54</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8139</v>
+        <v>0.4768</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3816</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>1.418</v>
+        <v>0.2604</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6157</v>
+        <v>0.9183</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1977</v>
+        <v>-0.6579</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9856</v>
+        <v>0.2796</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8017</v>
+        <v>-0.4415</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1839</v>
+        <v>0.7211</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2712</v>
+        <v>1.4858</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0385</v>
+        <v>1.0149</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7673</v>
+        <v>0.4709</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9384</v>
+        <v>-1.1786</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3491</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. THIAM PEDRERA</t>
+          <t>M. CARREIRA KREPS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1761</v>
+        <v>-0.2335</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2815</v>
+        <v>-0.7204</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1053</v>
+        <v>0.487</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7936</v>
+        <v>-1.5565</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8174</v>
+        <v>-0.2725</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-1.284</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.7967</v>
+        <v>-0.6545</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4019</v>
+        <v>0.0034</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3947</v>
+        <v>-0.6579</v>
       </c>
       <c r="M8" t="n">
-        <v>0.003</v>
+        <v>-0.902</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4154</v>
+        <v>-0.2759</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4184</v>
+        <v>-0.6261</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2068</v>
+        <v>0.091</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5152</v>
+        <v>-0.066</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6917</v>
+        <v>0.157</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. CARREIRA KREPS</t>
+          <t>O. THIAM PEDRERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3067</v>
+        <v>-0.2585</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6158</v>
+        <v>-1.2156</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3091</v>
+        <v>0.9571</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5565</v>
+        <v>-1.7936</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2725</v>
+        <v>-0.8174</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.284</v>
+        <v>-0.9762999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6545</v>
+        <v>-1.7967</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0034</v>
+        <v>-0.4019</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6579</v>
+        <v>-1.3947</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.902</v>
+        <v>0.003</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2759</v>
+        <v>-0.4154</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6261</v>
+        <v>0.4184</v>
       </c>
       <c r="P9" t="n">
-        <v>1.2321</v>
+        <v>0.4107</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2321</v>
+        <v>0.4107</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0177</v>
+        <v>1.1245</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0386</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0209</v>
+        <v>0.5434</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3938</v>
+        <v>-3.6427</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.6619</v>
+        <v>-5.1776</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2681</v>
+        <v>1.5349</v>
       </c>
       <c r="G10" t="n">
         <v>-5.8192</v>
@@ -1234,13 +1234,13 @@
         <v>2.4641</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9729</v>
+        <v>-0.2218</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.178</v>
+        <v>-0.6937</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2051</v>
+        <v>0.4719</v>
       </c>
       <c r="V10" t="n">
         <v>0.9609</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.2697</v>
+        <v>-7.875</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7139</v>
+        <v>-5.1711</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5558</v>
+        <v>-2.704</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6439</v>
@@ -1312,13 +1312,13 @@
         <v>0.8214</v>
       </c>
       <c r="S11" t="n">
-        <v>1.017</v>
+        <v>0.4116</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2749</v>
+        <v>-0.1823</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7421</v>
+        <v>0.5939</v>
       </c>
       <c r="V11" t="n">
         <v>-2.3573</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.7245</v>
+        <v>14.0538</v>
       </c>
       <c r="E12" t="n">
-        <v>4.9949</v>
+        <v>5.324300000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>8.7293</v>
+        <v>8.7296</v>
       </c>
       <c r="G12" t="n">
         <v>3.210599999999998</v>
@@ -1390,10 +1390,10 @@
         <v>15.4008</v>
       </c>
       <c r="S12" t="n">
-        <v>6.934799999999999</v>
+        <v>7.2642</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9742</v>
+        <v>2.3035</v>
       </c>
       <c r="U12" t="n">
         <v>4.9608</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6741</v>
+        <v>4.2808</v>
       </c>
       <c r="E13" t="n">
-        <v>4.1455</v>
+        <v>4.3547</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4714</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>2.738</v>
@@ -1468,13 +1468,13 @@
         <v>2.2588</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2343</v>
+        <v>-0.6276</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7673</v>
+        <v>-0.5581</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.467</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0.9384</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8139</v>
+        <v>2.1835</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6425</v>
+        <v>1.8517</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1714</v>
+        <v>0.3318</v>
       </c>
       <c r="G14" t="n">
         <v>2.0211</v>
@@ -1546,13 +1546,13 @@
         <v>1.6427</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.234</v>
+        <v>0.1356</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5115</v>
+        <v>-0.3023</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2776</v>
+        <v>0.4379</v>
       </c>
       <c r="V14" t="n">
         <v>-0.5893</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7893</v>
+        <v>0.7991</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5192</v>
+        <v>-0.6314</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2701</v>
+        <v>1.4305</v>
       </c>
       <c r="G15" t="n">
         <v>-1.1063</v>
@@ -1624,13 +1624,13 @@
         <v>3.2855</v>
       </c>
       <c r="S15" t="n">
-        <v>1.029</v>
+        <v>0.0387</v>
       </c>
       <c r="T15" t="n">
-        <v>1.069</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.04</v>
+        <v>0.1204</v>
       </c>
       <c r="V15" t="n">
         <v>-1.4189</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3404</v>
+        <v>0.4302</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2613</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6017</v>
+        <v>-0.1449</v>
       </c>
       <c r="G16" t="n">
         <v>-1.2923</v>
@@ -1702,13 +1702,13 @@
         <v>2.4641</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.8613</v>
+        <v>-1.0907</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3601</v>
+        <v>-1.0463</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5011</v>
+        <v>-0.0443</v>
       </c>
       <c r="V16" t="n">
         <v>0.3491</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.624</v>
+        <v>-1.4183</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7834</v>
+        <v>0.888</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4075</v>
+        <v>-2.3064</v>
       </c>
       <c r="G17" t="n">
         <v>0.3752</v>
@@ -1780,13 +1780,13 @@
         <v>1.4374</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8391</v>
+        <v>-0.6334</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7827</v>
+        <v>-0.6781</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0564</v>
+        <v>0.0447</v>
       </c>
       <c r="V17" t="n">
         <v>-2.5975</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0902</v>
+        <v>-1.8008</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4188</v>
+        <v>0.628</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5089</v>
+        <v>-2.4287</v>
       </c>
       <c r="G18" t="n">
         <v>1.1817</v>
@@ -1858,13 +1858,13 @@
         <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3684</v>
+        <v>-1.079</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9726</v>
+        <v>-0.7634</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3957</v>
+        <v>-0.3155</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2875</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.9759</v>
+        <v>-3.7475</v>
       </c>
       <c r="E19" t="n">
         <v>-2.4601</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5158</v>
+        <v>-1.2874</v>
       </c>
       <c r="G19" t="n">
         <v>-2.1135</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8357</v>
+        <v>-0.6073</v>
       </c>
       <c r="T19" t="n">
         <v>-0.527</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3087</v>
+        <v>-0.0803</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.1165</v>
+        <v>-5.8533</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.6079</v>
+        <v>-6.7125</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4914</v>
+        <v>0.8592</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6079</v>
@@ -2014,13 +2014,13 @@
         <v>2.2588</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6072</v>
+        <v>-0.3439</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1358</v>
+        <v>-0.2404</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4714</v>
+        <v>-0.1035</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.8547</v>
+        <v>-6.506</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.4322</v>
+        <v>-7.223</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5775</v>
+        <v>0.717</v>
       </c>
       <c r="G21" t="n">
         <v>-3.4066</v>
@@ -2092,13 +2092,13 @@
         <v>1.6427</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.984</v>
+        <v>-0.6353</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9726</v>
+        <v>-0.7634</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0114</v>
+        <v>0.1281</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-13.7244</v>
+        <v>-11.6323</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.7295</v>
+        <v>-8.729500000000002</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.9949</v>
+        <v>-2.9028</v>
       </c>
       <c r="G22" t="n">
         <v>-3.2106</v>
@@ -2170,13 +2170,13 @@
         <v>16.4274</v>
       </c>
       <c r="S22" t="n">
-        <v>-6.935</v>
+        <v>-4.842899999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-4.9606</v>
+        <v>-4.960599999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.9741</v>
+        <v>0.118</v>
       </c>
       <c r="V22" t="n">
         <v>-4.605700000000001</v>
